--- a/artfynd/A 7900-2026 artfynd.xlsx
+++ b/artfynd/A 7900-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131499834</v>
+        <v>131499794</v>
       </c>
       <c r="B2" t="n">
-        <v>79008</v>
+        <v>79869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363710</v>
+        <v>363821</v>
       </c>
       <c r="R2" t="n">
-        <v>6871721</v>
+        <v>6871793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131499794</v>
+        <v>131499826</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>79008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363821</v>
+        <v>363890</v>
       </c>
       <c r="R3" t="n">
-        <v>6871793</v>
+        <v>6871790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131499826</v>
+        <v>131499834</v>
       </c>
       <c r="B4" t="n">
         <v>79008</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363890</v>
+        <v>363710</v>
       </c>
       <c r="R4" t="n">
-        <v>6871790</v>
+        <v>6871721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1257,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131499807</v>
+        <v>131499836</v>
       </c>
       <c r="B8" t="n">
-        <v>79840</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363682</v>
+        <v>363827</v>
       </c>
       <c r="R8" t="n">
-        <v>6871697</v>
+        <v>6871708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1336,6 +1345,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1354,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131499806</v>
+        <v>131499807</v>
       </c>
       <c r="B9" t="n">
         <v>79840</v>
@@ -1389,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363671</v>
+        <v>363682</v>
       </c>
       <c r="R9" t="n">
-        <v>6871702</v>
+        <v>6871697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,43 +1461,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131499836</v>
+        <v>131499829</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1495,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363827</v>
+        <v>363822</v>
       </c>
       <c r="R10" t="n">
-        <v>6871708</v>
+        <v>6871771</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131499829</v>
+        <v>131499806</v>
       </c>
       <c r="B11" t="n">
-        <v>79008</v>
+        <v>79840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,37 +1573,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363822</v>
+        <v>363671</v>
       </c>
       <c r="R11" t="n">
-        <v>6871771</v>
+        <v>6871702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,7 +1641,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131499835</v>
+        <v>131499813</v>
       </c>
       <c r="B12" t="n">
-        <v>79008</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,34 +1670,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363684</v>
+        <v>363665</v>
       </c>
       <c r="R12" t="n">
-        <v>6871743</v>
+        <v>6871688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131499813</v>
+        <v>131499816</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,21 +1775,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1797,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1799,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>363665</v>
+        <v>363769</v>
       </c>
       <c r="R13" t="n">
-        <v>6871688</v>
+        <v>6871685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131499816</v>
+        <v>131499835</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>79008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,42 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>363769</v>
+        <v>363684</v>
       </c>
       <c r="R14" t="n">
-        <v>6871685</v>
+        <v>6871743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131499822</v>
+        <v>131499846</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>79007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,42 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>363666</v>
+        <v>363690</v>
       </c>
       <c r="R15" t="n">
-        <v>6871738</v>
+        <v>6871759</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131499846</v>
+        <v>131499858</v>
       </c>
       <c r="B16" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>363690</v>
+        <v>363751</v>
       </c>
       <c r="R16" t="n">
-        <v>6871759</v>
+        <v>6871722</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131499858</v>
+        <v>131499822</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,34 +2171,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363751</v>
+        <v>363666</v>
       </c>
       <c r="R17" t="n">
-        <v>6871722</v>
+        <v>6871738</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131499805</v>
+        <v>131499795</v>
       </c>
       <c r="B20" t="n">
-        <v>79840</v>
+        <v>79869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>363719</v>
+        <v>363706</v>
       </c>
       <c r="R20" t="n">
-        <v>6871720</v>
+        <v>6871649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131499795</v>
+        <v>131499805</v>
       </c>
       <c r="B21" t="n">
-        <v>79869</v>
+        <v>79840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,21 +2567,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>363706</v>
+        <v>363719</v>
       </c>
       <c r="R21" t="n">
-        <v>6871649</v>
+        <v>6871720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131499844</v>
+        <v>131499831</v>
       </c>
       <c r="B29" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3355,34 +3355,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>363719</v>
+        <v>363704</v>
       </c>
       <c r="R29" t="n">
-        <v>6871721</v>
+        <v>6871652</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,6 +3426,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3441,10 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131499831</v>
+        <v>131499844</v>
       </c>
       <c r="B30" t="n">
-        <v>79008</v>
+        <v>79007</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3452,37 +3456,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>363704</v>
+        <v>363719</v>
       </c>
       <c r="R30" t="n">
-        <v>6871652</v>
+        <v>6871721</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3523,7 +3524,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131499817</v>
+        <v>131499819</v>
       </c>
       <c r="B37" t="n">
-        <v>58047</v>
+        <v>57885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4159,21 +4159,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363762</v>
+        <v>363835</v>
       </c>
       <c r="R37" t="n">
-        <v>6871714</v>
+        <v>6871712</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131499819</v>
+        <v>131499817</v>
       </c>
       <c r="B38" t="n">
-        <v>57885</v>
+        <v>58047</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4286,7 +4286,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363835</v>
+        <v>363762</v>
       </c>
       <c r="R38" t="n">
-        <v>6871712</v>
+        <v>6871714</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131499811</v>
+        <v>131499830</v>
       </c>
       <c r="B39" t="n">
-        <v>79840</v>
+        <v>79008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,21 +4369,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363696</v>
+        <v>363770</v>
       </c>
       <c r="R39" t="n">
-        <v>6871769</v>
+        <v>6871686</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131499830</v>
+        <v>131499802</v>
       </c>
       <c r="B40" t="n">
-        <v>79008</v>
+        <v>79840</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,21 +4466,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131499802</v>
+        <v>131499811</v>
       </c>
       <c r="B41" t="n">
         <v>79840</v>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>363770</v>
+        <v>363696</v>
       </c>
       <c r="R41" t="n">
-        <v>6871686</v>
+        <v>6871769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131499796</v>
+        <v>131499809</v>
       </c>
       <c r="B43" t="n">
-        <v>79869</v>
+        <v>79840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>363760</v>
+        <v>363652</v>
       </c>
       <c r="R43" t="n">
-        <v>6871732</v>
+        <v>6871750</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131499809</v>
+        <v>131499798</v>
       </c>
       <c r="B44" t="n">
         <v>79840</v>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>363652</v>
+        <v>363900</v>
       </c>
       <c r="R44" t="n">
-        <v>6871750</v>
+        <v>6871805</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131499798</v>
+        <v>131499796</v>
       </c>
       <c r="B45" t="n">
-        <v>79840</v>
+        <v>79869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>363900</v>
+        <v>363760</v>
       </c>
       <c r="R45" t="n">
-        <v>6871805</v>
+        <v>6871732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 7900-2026 artfynd.xlsx
+++ b/artfynd/A 7900-2026 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131499832</v>
+        <v>131499841</v>
       </c>
       <c r="B5" t="n">
-        <v>79008</v>
+        <v>79007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363751</v>
+        <v>363890</v>
       </c>
       <c r="R5" t="n">
-        <v>6871723</v>
+        <v>6871790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131499841</v>
+        <v>131499832</v>
       </c>
       <c r="B6" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363890</v>
+        <v>363751</v>
       </c>
       <c r="R6" t="n">
-        <v>6871790</v>
+        <v>6871723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131499831</v>
+        <v>131499844</v>
       </c>
       <c r="B29" t="n">
-        <v>79008</v>
+        <v>79007</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3355,37 +3355,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>363704</v>
+        <v>363719</v>
       </c>
       <c r="R29" t="n">
-        <v>6871652</v>
+        <v>6871721</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,7 +3423,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3445,10 +3441,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131499844</v>
+        <v>131499831</v>
       </c>
       <c r="B30" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,34 +3452,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>363719</v>
+        <v>363704</v>
       </c>
       <c r="R30" t="n">
-        <v>6871721</v>
+        <v>6871652</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3524,6 +3523,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131499827</v>
+        <v>131499845</v>
       </c>
       <c r="B32" t="n">
-        <v>79008</v>
+        <v>79007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3658,34 +3658,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>363832</v>
+        <v>363686</v>
       </c>
       <c r="R32" t="n">
-        <v>6871779</v>
+        <v>6871754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,6 +3729,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3744,10 +3748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131499801</v>
+        <v>131499827</v>
       </c>
       <c r="B33" t="n">
-        <v>79840</v>
+        <v>79008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,37 +3759,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>363844</v>
+        <v>363832</v>
       </c>
       <c r="R33" t="n">
-        <v>6871725</v>
+        <v>6871779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3826,7 +3827,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131499845</v>
+        <v>131499801</v>
       </c>
       <c r="B34" t="n">
-        <v>79007</v>
+        <v>79840</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3856,21 +3856,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363686</v>
+        <v>363844</v>
       </c>
       <c r="R34" t="n">
-        <v>6871754</v>
+        <v>6871725</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 7900-2026 artfynd.xlsx
+++ b/artfynd/A 7900-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131499794</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131499826</v>
       </c>
       <c r="B3" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131499834</v>
       </c>
       <c r="B4" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131499841</v>
       </c>
       <c r="B5" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131499832</v>
       </c>
       <c r="B6" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131499842</v>
       </c>
       <c r="B7" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>131499836</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131499807</v>
+        <v>131499806</v>
       </c>
       <c r="B9" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363682</v>
+        <v>363671</v>
       </c>
       <c r="R9" t="n">
-        <v>6871697</v>
+        <v>6871702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131499829</v>
+        <v>131499807</v>
       </c>
       <c r="B10" t="n">
-        <v>79008</v>
+        <v>79843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,37 +1472,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363822</v>
+        <v>363682</v>
       </c>
       <c r="R10" t="n">
-        <v>6871771</v>
+        <v>6871697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1543,7 +1540,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131499806</v>
+        <v>131499829</v>
       </c>
       <c r="B11" t="n">
-        <v>79840</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,34 +1569,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363671</v>
+        <v>363822</v>
       </c>
       <c r="R11" t="n">
-        <v>6871702</v>
+        <v>6871771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1640,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131499813</v>
+        <v>131499835</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,42 +1670,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363665</v>
+        <v>363684</v>
       </c>
       <c r="R12" t="n">
-        <v>6871688</v>
+        <v>6871743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131499816</v>
+        <v>131499813</v>
       </c>
       <c r="B13" t="n">
-        <v>58047</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1775,21 +1767,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,7 +1789,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1807,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>363769</v>
+        <v>363665</v>
       </c>
       <c r="R13" t="n">
-        <v>6871685</v>
+        <v>6871688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1869,10 +1861,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131499835</v>
+        <v>131499816</v>
       </c>
       <c r="B14" t="n">
-        <v>79008</v>
+        <v>58050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1872,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>363684</v>
+        <v>363769</v>
       </c>
       <c r="R14" t="n">
-        <v>6871743</v>
+        <v>6871685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>131499846</v>
       </c>
       <c r="B15" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>131499858</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>131499822</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>131499804</v>
       </c>
       <c r="B18" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>131499833</v>
       </c>
       <c r="B19" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>131499795</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>131499805</v>
       </c>
       <c r="B21" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131499803</v>
+        <v>131499857</v>
       </c>
       <c r="B22" t="n">
-        <v>79840</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>363739</v>
+        <v>363771</v>
       </c>
       <c r="R22" t="n">
-        <v>6871721</v>
+        <v>6871701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131499857</v>
+        <v>131499803</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79843</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>363771</v>
+        <v>363739</v>
       </c>
       <c r="R23" t="n">
-        <v>6871701</v>
+        <v>6871721</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
         <v>131499810</v>
       </c>
       <c r="B24" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>131499843</v>
       </c>
       <c r="B25" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>131499859</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>131499823</v>
       </c>
       <c r="B27" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131499800</v>
       </c>
       <c r="B28" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>131499844</v>
       </c>
       <c r="B29" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>131499831</v>
       </c>
       <c r="B30" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>131499812</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>131499845</v>
       </c>
       <c r="B32" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131499827</v>
+        <v>131499801</v>
       </c>
       <c r="B33" t="n">
-        <v>79008</v>
+        <v>79843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3759,34 +3759,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>363832</v>
+        <v>363844</v>
       </c>
       <c r="R33" t="n">
-        <v>6871779</v>
+        <v>6871725</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3827,6 +3830,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3845,10 +3849,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131499801</v>
+        <v>131499827</v>
       </c>
       <c r="B34" t="n">
-        <v>79840</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3856,37 +3860,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363844</v>
+        <v>363832</v>
       </c>
       <c r="R34" t="n">
-        <v>6871725</v>
+        <v>6871779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3927,7 +3928,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>131499828</v>
       </c>
       <c r="B35" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4043,32 +4043,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131499838</v>
+        <v>131499817</v>
       </c>
       <c r="B36" t="n">
-        <v>58260</v>
+        <v>58050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>363731</v>
+        <v>363762</v>
       </c>
       <c r="R36" t="n">
-        <v>6871683</v>
+        <v>6871714</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4151,7 +4151,7 @@
         <v>131499819</v>
       </c>
       <c r="B37" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,32 +4253,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131499817</v>
+        <v>131499838</v>
       </c>
       <c r="B38" t="n">
-        <v>58047</v>
+        <v>58263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363762</v>
+        <v>363731</v>
       </c>
       <c r="R38" t="n">
-        <v>6871714</v>
+        <v>6871683</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131499830</v>
+        <v>131499818</v>
       </c>
       <c r="B39" t="n">
-        <v>79008</v>
+        <v>57888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,34 +4369,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363770</v>
+        <v>363825</v>
       </c>
       <c r="R39" t="n">
-        <v>6871686</v>
+        <v>6871738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4458,7 +4466,7 @@
         <v>131499802</v>
       </c>
       <c r="B40" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,7 +4563,7 @@
         <v>131499811</v>
       </c>
       <c r="B41" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,10 +4657,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131499818</v>
+        <v>131499830</v>
       </c>
       <c r="B42" t="n">
-        <v>57885</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,42 +4668,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>363825</v>
+        <v>363770</v>
       </c>
       <c r="R42" t="n">
-        <v>6871738</v>
+        <v>6871686</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
         <v>131499809</v>
       </c>
       <c r="B43" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>131499798</v>
       </c>
       <c r="B44" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131499796</v>
+        <v>131499820</v>
       </c>
       <c r="B45" t="n">
-        <v>79869</v>
+        <v>57888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,34 +4959,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>363760</v>
+        <v>363747</v>
       </c>
       <c r="R45" t="n">
-        <v>6871732</v>
+        <v>6871736</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5045,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131499820</v>
+        <v>131499796</v>
       </c>
       <c r="B46" t="n">
-        <v>57885</v>
+        <v>79872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5056,42 +5064,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>363747</v>
+        <v>363760</v>
       </c>
       <c r="R46" t="n">
-        <v>6871736</v>
+        <v>6871732</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5153,7 +5153,7 @@
         <v>131499808</v>
       </c>
       <c r="B47" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>131499799</v>
       </c>
       <c r="B48" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 7900-2026 artfynd.xlsx
+++ b/artfynd/A 7900-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131499794</v>
+        <v>131499826</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>79012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363821</v>
+        <v>363890</v>
       </c>
       <c r="R2" t="n">
-        <v>6871793</v>
+        <v>6871790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131499826</v>
+        <v>131499834</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363890</v>
+        <v>363710</v>
       </c>
       <c r="R3" t="n">
-        <v>6871790</v>
+        <v>6871721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131499834</v>
+        <v>131499794</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363710</v>
+        <v>363821</v>
       </c>
       <c r="R4" t="n">
-        <v>6871721</v>
+        <v>6871793</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>131499841</v>
       </c>
       <c r="B5" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>131499832</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>131499842</v>
       </c>
       <c r="B7" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>131499806</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>131499807</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>131499829</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131499835</v>
+        <v>131499813</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,34 +1670,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363684</v>
+        <v>363665</v>
       </c>
       <c r="R12" t="n">
-        <v>6871743</v>
+        <v>6871688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131499813</v>
+        <v>131499816</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>58051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1767,21 +1775,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1797,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1799,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>363665</v>
+        <v>363769</v>
       </c>
       <c r="R13" t="n">
-        <v>6871688</v>
+        <v>6871685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131499816</v>
+        <v>131499835</v>
       </c>
       <c r="B14" t="n">
-        <v>58050</v>
+        <v>79012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,42 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>363769</v>
+        <v>363684</v>
       </c>
       <c r="R14" t="n">
-        <v>6871685</v>
+        <v>6871743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131499846</v>
+        <v>131499822</v>
       </c>
       <c r="B15" t="n">
-        <v>79010</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1977,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>363690</v>
+        <v>363666</v>
       </c>
       <c r="R15" t="n">
-        <v>6871759</v>
+        <v>6871738</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131499858</v>
+        <v>131499846</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2082,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>363751</v>
+        <v>363690</v>
       </c>
       <c r="R16" t="n">
-        <v>6871722</v>
+        <v>6871759</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2168,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131499822</v>
+        <v>131499858</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,42 +2179,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363666</v>
+        <v>363751</v>
       </c>
       <c r="R17" t="n">
-        <v>6871738</v>
+        <v>6871722</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131499804</v>
+        <v>131499833</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>79012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>363731</v>
+        <v>363719</v>
       </c>
       <c r="R18" t="n">
-        <v>6871712</v>
+        <v>6871721</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131499833</v>
+        <v>131499804</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>363719</v>
+        <v>363731</v>
       </c>
       <c r="R19" t="n">
-        <v>6871721</v>
+        <v>6871712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
         <v>131499795</v>
       </c>
       <c r="B20" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>131499805</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>131499857</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>131499803</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>131499810</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>131499843</v>
       </c>
       <c r="B25" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>131499859</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>131499823</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>131499800</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>131499844</v>
       </c>
       <c r="B29" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>131499831</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>131499812</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>131499845</v>
       </c>
       <c r="B32" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131499801</v>
+        <v>131499827</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>79012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3759,37 +3759,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>363844</v>
+        <v>363832</v>
       </c>
       <c r="R33" t="n">
-        <v>6871725</v>
+        <v>6871779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,7 +3827,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3849,10 +3845,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131499827</v>
+        <v>131499801</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3860,34 +3856,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363832</v>
+        <v>363844</v>
       </c>
       <c r="R34" t="n">
-        <v>6871779</v>
+        <v>6871725</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3928,6 +3927,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>131499828</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>131499817</v>
       </c>
       <c r="B36" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4148,27 +4148,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131499819</v>
+        <v>131499838</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>58264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4181,7 +4181,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363835</v>
+        <v>363731</v>
       </c>
       <c r="R37" t="n">
-        <v>6871712</v>
+        <v>6871683</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,27 +4253,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131499838</v>
+        <v>131499819</v>
       </c>
       <c r="B38" t="n">
-        <v>58263</v>
+        <v>57889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363731</v>
+        <v>363835</v>
       </c>
       <c r="R38" t="n">
-        <v>6871683</v>
+        <v>6871712</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131499818</v>
+        <v>131499802</v>
       </c>
       <c r="B39" t="n">
-        <v>57888</v>
+        <v>79844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,42 +4369,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363825</v>
+        <v>363770</v>
       </c>
       <c r="R39" t="n">
-        <v>6871738</v>
+        <v>6871686</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4463,10 +4455,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131499802</v>
+        <v>131499830</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>79012</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4474,21 +4466,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4563,7 +4555,7 @@
         <v>131499811</v>
       </c>
       <c r="B41" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4657,10 +4649,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131499830</v>
+        <v>131499818</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>57889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4668,34 +4660,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>363770</v>
+        <v>363825</v>
       </c>
       <c r="R42" t="n">
-        <v>6871686</v>
+        <v>6871738</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
         <v>131499809</v>
       </c>
       <c r="B43" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>131499798</v>
       </c>
       <c r="B44" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>131499820</v>
       </c>
       <c r="B45" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>131499796</v>
       </c>
       <c r="B46" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131499808</v>
       </c>
       <c r="B47" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>131499799</v>
       </c>
       <c r="B48" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 7900-2026 artfynd.xlsx
+++ b/artfynd/A 7900-2026 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131499841</v>
+        <v>131499832</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363890</v>
+        <v>363751</v>
       </c>
       <c r="R5" t="n">
-        <v>6871790</v>
+        <v>6871723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131499832</v>
+        <v>131499841</v>
       </c>
       <c r="B6" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363751</v>
+        <v>363890</v>
       </c>
       <c r="R6" t="n">
-        <v>6871723</v>
+        <v>6871790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131499843</v>
+        <v>131499859</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>363749</v>
+        <v>363635</v>
       </c>
       <c r="R25" t="n">
-        <v>6871725</v>
+        <v>6871757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131499859</v>
+        <v>131499843</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,21 +3052,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>363635</v>
+        <v>363749</v>
       </c>
       <c r="R26" t="n">
-        <v>6871757</v>
+        <v>6871725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131499802</v>
+        <v>131499818</v>
       </c>
       <c r="B39" t="n">
-        <v>79844</v>
+        <v>57889</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,34 +4369,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363770</v>
+        <v>363825</v>
       </c>
       <c r="R39" t="n">
-        <v>6871686</v>
+        <v>6871738</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131499830</v>
+        <v>131499802</v>
       </c>
       <c r="B40" t="n">
-        <v>79012</v>
+        <v>79844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,21 +4474,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4552,10 +4560,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131499811</v>
+        <v>131499830</v>
       </c>
       <c r="B41" t="n">
-        <v>79844</v>
+        <v>79012</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,21 +4571,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4587,10 +4595,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>363696</v>
+        <v>363770</v>
       </c>
       <c r="R41" t="n">
-        <v>6871769</v>
+        <v>6871686</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,10 +4657,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131499818</v>
+        <v>131499811</v>
       </c>
       <c r="B42" t="n">
-        <v>57889</v>
+        <v>79844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,42 +4668,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>363825</v>
+        <v>363696</v>
       </c>
       <c r="R42" t="n">
-        <v>6871738</v>
+        <v>6871769</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
